--- a/public/templates/000_pm_suite/프로젝트관리(Project Management) 용어 해설_V1_0.xlsx
+++ b/public/templates/000_pm_suite/프로젝트관리(Project Management) 용어 해설_V1_0.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="1449">
   <si>
-    <t>NO</t>
+    <t>NO [주식회사 엠파시 · 한빛글로벌 SyncGuard AI 표준]</t>
   </si>
   <si>
     <t>영문용어</t>

--- a/public/templates/000_pm_suite/프로젝트관리(Project Management) 용어 해설_V1_0.xlsx
+++ b/public/templates/000_pm_suite/프로젝트관리(Project Management) 용어 해설_V1_0.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="1449">
   <si>
-    <t>NO [주식회사 엠파시 · 한빛글로벌 SyncGuard AI 표준]</t>
+    <t>NO [주식회사 엠파시 · 한빛글로벌 SyncFlow AI 표준]</t>
   </si>
   <si>
     <t>영문용어</t>
@@ -110,7 +110,7 @@
     <t>활동 기술</t>
   </si>
   <si>
-    <t>프로젝트의 각 일정 활동을 다른 일정과 구별하기 위해 활동식별코드와 함께 사용하는 각 일정 활동의 표지 또는 간결한 설명 문구. 활동 기술은 일반적으로 일정 활동의 작업 범위를 설명한다.</t>
+    <t>프로젝트의 각 일정 활동을 다른 일정과 구별하기 위해 활동식별코드와 함께 사용하는 각 일정 활동의 표지 또는 간결한 설명 조항. 활동 기술은 일반적으로 일정 활동의 작업 범위를 설명한다.</t>
   </si>
   <si>
     <t>Activity Duration</t>
@@ -317,7 +317,7 @@
     <t>가정</t>
   </si>
   <si>
-    <t>기획 목적으로, 증거 또는 실증 없이 사실이거나 확실한 것으로 간주하는 요소들로, 프로젝트 기획의 모든 면에 영향을 미치며 프로젝트의 점진적 구체화의 한 부분이다프로젝트팀은 프로세스 기획의 일환으로 빈번하게 가정을 식별하여 문서화하고 검증한다일반적으로 가정에는 어느 정도의 리스크가 수반된다.</t>
+    <t>기획 목적으로, 증거 또는 시험검증 없이 사실이거나 확실한 것으로 간주하는 요소들로, 프로젝트 기획의 모든 면에 영향을 미치며 프로젝트의 점진적 구체화의 한 부분이다프로젝트팀은 프로세스 기획의 일환으로 빈번하게 가정을 식별하여 문서화하고 검증한다일반적으로 가정에는 어느 정도의 리스크가 수반된다.</t>
   </si>
   <si>
     <t>Assumptions Analysis</t>
@@ -365,7 +365,7 @@
     <t>기준선</t>
   </si>
   <si>
-    <t>프로젝트, 작업분류체계 구성요소, 작업 패키지 또는 일정 활동 등에 대하여 승인된 시차별 계획에 승인된 프로젝트 범위, 원가, 일정 및 기술적 변경 사항을 가감한 것일반적으로 현재 기준선을 의미하지만 초기 기준선이나 일부 다른 기준선을 나타낼 수도 있고, 수식 어구와 함께 사용된다(예: 원가 기준선, 일정 기준선, 성과 측정 기준선, 기술적 기준선)성과 측정 기준선 참조.</t>
+    <t>프로젝트, 작업분류체계 구성요소, 작업 도면패키지 또는 일정 활동 등에 대하여 승인된 시차별 계획에 승인된 프로젝트 범위, 원가, 일정 및 기술적 변경 사항을 가감한 것일반적으로 현재 기준선을 의미하지만 초기 기준선이나 일부 다른 기준선을 나타낼 수도 있고, 수식 어구와 함께 사용된다(예: 원가 기준선, 일정 기준선, 성과 측정 기준선, 기술적 기준선)성과 측정 기준선 참조.</t>
   </si>
   <si>
     <t>Baseline Finish Date</t>
@@ -539,7 +539,7 @@
     <t>누락됨 없이 연관된 활동들의 적절한 관리를 유지하거나 간편한 비교를 위해 모두 열거해 놓은 항목표품질기획 단계에서 작성하여 품질통제에 적용하는 검사 대상 항목 목록이 점검목록의 한 가지 예이다.</t>
   </si>
   <si>
-    <t>Claim</t>
+    <t>Spec</t>
   </si>
   <si>
     <t>청구</t>
@@ -743,7 +743,7 @@
     <t>통제단위</t>
   </si>
   <si>
-    <t>범위, 예산, 실제원가 및 일정의 통합이 일어나고 성과 측정이 진행될 관리 통제 지점통제단위는 작업분류체계상에서 선택된 관리 지점(지정된 수준의 특정한 구성요소)에 배정된다각 통제단위에 하나 이상의 작업 패키지가 포함될 수 있지만 각 작업 패키지와 연관될 수 있는 통제단위는 한 개 뿐이며, 각 통제단위는 조직분류체계(OBS)의 특정 조직 구성요소 단 한 개와 연결된다전에는 원가계정이라고 했다 작업 패키지 참조.</t>
+    <t>범위, 예산, 실제원가 및 일정의 통합이 일어나고 성과 측정이 진행될 관리 통제 지점통제단위는 작업분류체계상에서 선택된 관리 지점(지정된 수준의 특정한 구성요소)에 배정된다각 통제단위에 하나 이상의 작업 도면패키지가 포함될 수 있지만 각 작업 도면패키지와 연관될 수 있는 통제단위는 한 개 뿐이며, 각 통제단위는 조직분류체계(OBS)의 특정 조직 구성요소 단 한 개와 연결된다전에는 원가계정이라고 했다 작업 도면패키지 참조.</t>
   </si>
   <si>
     <t>Control Account Plan (CAP)</t>
@@ -812,7 +812,7 @@
     <t>원가예산책정</t>
   </si>
   <si>
-    <t>원가 기준선을 설정하기 위해 개별 활동이나 작업 패키지의 산정 원가를 모두 합산하는 프로세스.</t>
+    <t>원가 기준선을 설정하기 위해 개별 활동이나 작업 도면패키지의 산정 원가를 모두 합산하는 프로세스.</t>
   </si>
   <si>
     <t>Cost Control</t>
@@ -2078,7 +2078,7 @@
     <t>조직분류체계</t>
   </si>
   <si>
-    <t>작업 패키지가 수행 조직 팀에 연결되도록 배열한 프로젝트 구성 계통도OBS(Organizational Breakdown Structure) 대신 약어가 같은 OBS(Organization Breakdown Structure)를 사용하기도 한다.</t>
+    <t>작업 도면패키지가 수행 조직 팀에 연결되도록 배열한 프로젝트 구성 계통도OBS(Organizational Breakdown Structure) 대신 약어가 같은 OBS(Organization Breakdown Structure)를 사용하기도 한다.</t>
   </si>
   <si>
     <t>Organizational Process Assets</t>
@@ -2267,7 +2267,7 @@
     <t>Planning Package</t>
   </si>
   <si>
-    <t>기획 패키지</t>
+    <t>기획 도면패키지</t>
   </si>
   <si>
     <t>상세한 일정 활동은 없지만 작업 내용이 이미 파악된 통제단위 아래쪽의 WBS 구성요소통제단위 참조.</t>
@@ -2576,7 +2576,7 @@
     <t>프로젝트관리 지식체계</t>
   </si>
   <si>
-    <t>프로젝트관리 전문 분야의 총체적 지식을 설명하는 포괄적인 용어법률, 의약품, 회계 등과 같은 다른 전문 분야와 마찬가지로 프로젝트관리 지식체계 또한 그것을 적용하고 향상시키는 실무자와 연구원에게 달려 있다완전한 PMBOK에는 널리 적용되고 있는 입증된 기존의 실무 사례는 물론 보다 혁신적이고 전문성 있는 실무 관행도 포함된다PMBOK은 출판된 형태와 출판되지 않은 형태 모두 존재하며, 끊임없이 발전되고 있다.</t>
+    <t>프로젝트관리 전문 분야의 총체적 지식을 설명하는 포괄적인 용어법률, 불공정특약, 회계 등과 같은 다른 전문 분야와 마찬가지로 프로젝트관리 지식체계 또한 그것을 적용하고 향상시키는 실무자와 연구원에게 달려 있다완전한 PMBOK에는 널리 적용되고 있는 입증된 기존의 실무 사례는 물론 보다 혁신적이고 전문성 있는 실무 관행도 포함된다PMBOK은 출판된 형태와 출판되지 않은 형태 모두 존재하며, 끊임없이 발전되고 있다.</t>
   </si>
   <si>
     <t>Project Management Information System (PMIS)</t>
@@ -3272,7 +3272,7 @@
     <t>일정 활동</t>
   </si>
   <si>
-    <t>프로젝트 진행 과정에서 수행되는 작업에서 개별적으로 일정이 지정된 작업 구성요소일정 활동에는 일반적으로 산정 기간, 산정 원가, 산정 자원 요구 사항이 명시되어 있다일정이 지정된 활동은 다른 일정 활동이나 일정 마일스톤에 논리적 관계로 연결되며, 작업 패키지에서 분할된다.</t>
+    <t>프로젝트 진행 과정에서 수행되는 작업에서 개별적으로 일정이 지정된 작업 구성요소일정 활동에는 일반적으로 산정 기간, 산정 원가, 산정 자원 요구 사항이 명시되어 있다일정이 지정된 활동은 다른 일정 활동이나 일정 마일스톤에 논리적 관계로 연결되며, 작업 도면패키지에서 분할된다.</t>
   </si>
   <si>
     <t>Schedule Analysis</t>
@@ -3650,7 +3650,7 @@
     <t>하부 네트워크</t>
   </si>
   <si>
-    <t>프로젝트 일정 네트워크도의 세분화된 구간(단편)으로, 보통 하부 프로젝트 또는 작업 패키지를 나타낸다종종 우선되는 논리 또는 프로젝트 범위 변경과 같은 일부 잠재적 또는 제안된 일정 조건을 살펴보거나 연구하는 데 사용된다.</t>
+    <t>프로젝트 일정 네트워크도의 세분화된 구간(단편)으로, 보통 하부 프로젝트 또는 작업 도면패키지를 나타낸다종종 우선되는 논리 또는 프로젝트 범위 변경과 같은 일부 잠재적 또는 제안된 일정 조건을 살펴보거나 연구하는 데 사용된다.</t>
   </si>
   <si>
     <t>Subphase</t>
@@ -3992,7 +3992,7 @@
     <t>작업승인</t>
   </si>
   <si>
-    <t>특정한 일정 활동 또는 작업 패키지, 통제단위의 작업을 개시하는 권한 및 재량서면 형태의 허가서가 일반적이며, 작업이 담당 조직에 의해 올바른 시간에 적절한 순서로 수행될 수 있도록 프로젝트 작업을 인가하는 방식이다.</t>
+    <t>특정한 일정 활동 또는 작업 도면패키지, 통제단위의 작업을 개시하는 권한 및 재량서면 형태의 허가서가 일반적이며, 작업이 담당 조직에 의해 올바른 시간에 적절한 순서로 수행될 수 있도록 프로젝트 작업을 인가하는 방식이다.</t>
   </si>
   <si>
     <t>Work Authorization System</t>
@@ -4010,7 +4010,7 @@
     <t>작업분류체계</t>
   </si>
   <si>
-    <t>프로젝트 팀이 프로젝트 목표를 달성하고 필요한 인도물을 산출하기 위해 실행하는 작업을 인도물 중심의 계층 구조로 세분해 놓은 것프로젝트의 전체 범위를 구성하고 정의하며, 하위수준으로 내려가면서 프로젝트 작업에 대해 점차 상세한 정의를 보여준다WBS는 작업 패키지로 세분되고, 인도물 중심으로 구성되며 내부 인도물과 외부 인도물을 모두 포함하고 있다작업 패키지, 통제단위, 계약 작업분류체계 및 프로젝트 요약 작업분류체계 참조.</t>
+    <t>프로젝트 팀이 프로젝트 목표를 달성하고 필요한 인도물을 산출하기 위해 실행하는 작업을 인도물 중검증 계층 구조로 세분해 놓은 것프로젝트의 전체 범위를 구성하고 정의하며, 하위수준으로 내려가면서 프로젝트 작업에 대해 점차 상세한 정의를 보여준다WBS는 작업 도면패키지로 세분되고, 인도물 중심으로 구성되며 내부 인도물과 외부 인도물을 모두 포함하고 있다작업 도면패키지, 통제단위, 계약 작업분류체계 및 프로젝트 요약 작업분류체계 참조.</t>
   </si>
   <si>
     <t>Work Breakdown Structure Component</t>
@@ -4043,10 +4043,10 @@
     <t>Work Package</t>
   </si>
   <si>
-    <t>작업 패키지</t>
-  </si>
-  <si>
-    <t>작업분류체계의 각 분기에서 최하위 수준에 있는 인도물이나 프로젝트 작업 구성요소작업 패키지에는 작업 패키지 인도물이나 프로젝트 작업 구성요소를 완료하는 데 필요한 일정 활동 및 일정 마일스톤이 포함된다통제단위 참조.</t>
+    <t>작업 도면패키지</t>
+  </si>
+  <si>
+    <t>작업분류체계의 각 분기에서 최하위 수준에 있는 인도물이나 프로젝트 작업 구성요소작업 도면패키지에는 작업 도면패키지 인도물이나 프로젝트 작업 구성요소를 완료하는 데 필요한 일정 활동 및 일정 마일스톤이 포함된다통제단위 참조.</t>
   </si>
   <si>
     <t>Work Performance Information</t>
